--- a/template/견적서.xlsx
+++ b/template/견적서.xlsx
@@ -10,165 +10,159 @@
     <sheet name="견적서" sheetId="19" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">견적서!$A$1:$F$37</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">견적서!$A$1:$F$38</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="48">
   <si>
     <t xml:space="preserve">견   적   서 </t>
   </si>
   <si>
+    <t xml:space="preserve"> 수신 : {{거래처명 현장명}} 귀중</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 참조 : {{담당자}} 귀하</t>
   </si>
   <si>
+    <t xml:space="preserve"> 견적일자 : {{견적일자}}</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 사업자번호 : 120-86-30516 </t>
   </si>
   <si>
-    <t xml:space="preserve"> 견적일자 : {{견적일자}}</t>
+    <t xml:space="preserve"> 납품기한 : 협의후 조정</t>
   </si>
   <si>
     <t xml:space="preserve"> 법인명 : ㈜오픈웍스 </t>
   </si>
   <si>
-    <t xml:space="preserve"> 납품기한 : 협의후 조정</t>
+    <t xml:space="preserve"> 납품장소 : 지정장소</t>
   </si>
   <si>
     <t xml:space="preserve"> TEL : 031-528-4400</t>
   </si>
   <si>
-    <t xml:space="preserve"> 납품장소 : 지정장소</t>
+    <t xml:space="preserve"> 견적명 : {{견적명}}</t>
   </si>
   <si>
     <t xml:space="preserve"> FAX : 031-528-4405</t>
   </si>
   <si>
+    <t>(1){{TOP_GROUP_1}}</t>
+  </si>
+  <si>
     <t xml:space="preserve"> www.openworks.co.kr</t>
   </si>
   <si>
-    <t>(1){{TOP_GROUP_1}}</t>
-  </si>
-  <si>
     <t>{{ITEM_START}}</t>
   </si>
   <si>
     <t>(단위 : 원)</t>
   </si>
   <si>
+    <t>구  분</t>
+  </si>
+  <si>
+    <t>세부사양</t>
+  </si>
+  <si>
+    <t>공급단가</t>
+  </si>
+  <si>
+    <t>수량</t>
+  </si>
+  <si>
+    <t>공급가액</t>
+  </si>
+  <si>
+    <t>비 고</t>
+  </si>
+  <si>
     <t>{{HEADER_ROW}}</t>
   </si>
   <si>
+    <t xml:space="preserve"> {{GROUP_TITLE}} {{name}}</t>
+  </si>
+  <si>
+    <t>※ 적용사유 : 중대재해 처벌법 시행에 따른 작업자 안전관리 강화 및 재해사고 방지를 위한 필수적용</t>
+  </si>
+  <si>
+    <t>{{SAFETY_NOTE_ROW}}</t>
+  </si>
+  <si>
+    <t>※ 적용기준 : 시공팀 판단하에 작업필요시마다 건별 필수적용(최초 설치 이후부터 건별적용 / 현장지원 불가시 별도 비용협의)</t>
+  </si>
+  <si>
+    <t>{{ITEM_ROW}}</t>
+  </si>
+  <si>
+    <t>소계</t>
+  </si>
+  <si>
+    <t>{{SUBTOTAL_ROW}}</t>
+  </si>
+  <si>
+    <t>합   계</t>
+  </si>
+  <si>
+    <t>VAT별도</t>
+  </si>
+  <si>
+    <t>{{GRAND_TOTAL}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ◆ 견적 특수조건  [ Terms and Conditions ]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1. 하자보증 : 최초 설치일로부터 12개월간 무상 진행 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">    ※ 무상지원항목 : 원격기술지원, 원격점검, 원격고객응대 등은 준공시까지 무상 진행</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    ※ 예외사항① : 천재지변, 고객취급 부주의에 의한 파손, 고장시는 실비 정산    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">    ※ 예외사항② : 안전관리 필수항목은 작업필요시마다 건별 필수적용 (최초 설치 이후부터 건별적용 / 현장지원 불가시 별도 비용협의)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2. 시스템 운영에 필요한 관리비(통신,전기,건물임대비 등) 납부는 현장 지원사항입니다. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">    ※ 고객사 명의 및 납부(현장사무실 지로 청구 예정)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    ※ 고객사 명의로 진행 불가시 관련 비용 견적에 반영</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 3. 세부실사 후 현장 여건에 따라 상기 견적외 추가공사 및 장비, 자재가 필요할 수 있습니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4. 공사 중 환경 변화 및 현장 여건에 따라 상기 견적외 추가공사 및 장비, 자재가 필요할 수 있습니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 5. 시스템 설치 및 통신장비 구축, 배선공사 등에 관련하여, 기존 시설물(건물, 가로등, 사유지 등)의 협의 필요 시 현장지원이 필요할 수 있습니다.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 6. 중대재해처벌법 시행에 따라 고소작업 시 스카이크레인, 리프트, 차징카 지원 등이 필요할 수 있습니다. (현장지원 불가시 별도 비용협의가 필요합니다.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> {{SPECIAL_NOTE:7}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> {{AFTER_NOTE_NUM}}. 상기 견적항목 외 현장의 추가요청 사항이 있을 시 모든 사항은 별도 협의가 필요합니다.</t>
+  </si>
+  <si>
+    <t>{{EMPTY_ROW}}</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
     <t>{{ITEM_END}}</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ◆ 견적 특수조건  [ Terms and Conditions ]</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 1. 하자보증 : 최초 설치일로부터 12개월간 무상 진행 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">    ※ 무상지원항목 : 원격기술지원, 원격점검, 원격고객응대 등은 준공시까지 무상 진행</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    ※ 예외사항① : 천재지변, 고객취급 부주의에 의한 파손, 고장시는 실비 정산    </t>
-  </si>
-  <si>
-    <t xml:space="preserve">    ※ 예외사항② : 안전관리 필수항목은 작업필요시마다 건별 필수적용 (최초 설치 이후부터 건별적용 / 현장지원 불가시 별도 비용협의)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 2. 시스템 운영에 필요한 관리비(통신,전기,건물임대비 등) 납부는 현장 지원사항입니다. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">    ※ 고객사 명의 및 납부(현장사무실 지로 청구 예정)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    ※ 고객사 명의로 진행 불가시 관련 비용 견적에 반영</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 3. 세부실사 후 현장 여건에 따라 상기 견적외 추가공사 및 장비, 자재가 필요할 수 있습니다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 4. 공사 중 환경 변화 및 현장 여건에 따라 상기 견적외 추가공사 및 장비, 자재가 필요할 수 있습니다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 5. 시스템 설치 및 통신장비 구축, 배선공사 등에 관련하여, 기존 시설물(건물, 가로등, 사유지 등)의 협의 필요 시 현장지원이 필요할 수 있습니다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 6. 중대재해처벌법 시행에 따라 고소작업 시 스카이크레인, 리프트, 차징카 지원 등이 필요할 수 있습니다. (현장지원 불가시 별도 비용협의가 필요합니다.)</t>
-  </si>
-  <si>
-    <t>{{EMPTY_ROW}}</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>소계</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>비 고</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>공급가액</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>수량</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>공급단가</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>세부사양</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>구  분</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>{{SUBTOTAL_ROW}}</t>
-  </si>
-  <si>
-    <t>VAT별도</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>{{GRAND_TOTAL}}</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>합   계</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> {{AFTER_NOTE_NUM}}. 상기 견적항목 외 현장의 추가요청 사항이 있을 시 모든 사항은 별도 협의가 필요합니다.</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> {{SPECIAL_NOTE:7}}</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> 견적명 : {{견적명}}</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> 수신 : {{거래처명 현장명}} 귀중</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>{{ITEM_ROW}}</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> {{GROUP_TITLE}} {{name}}</t>
-    <phoneticPr fontId="14" type="noConversion"/>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -178,7 +172,7 @@
   <numFmts count="1">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -268,6 +262,12 @@
       <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -312,7 +312,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -350,17 +350,6 @@
     </border>
     <border>
       <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right style="thin">
         <color indexed="64"/>
       </right>
@@ -381,11 +370,35 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -423,16 +436,28 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="41" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -441,74 +466,68 @@
     <xf numFmtId="41" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="41" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="10" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="10" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -739,8 +758,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13031675" y="4286250"/>
-          <a:ext cx="721001" cy="666623"/>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -783,8 +802,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10653432" y="3092824"/>
-          <a:ext cx="1695912" cy="861973"/>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -827,8 +846,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12370447" y="3279344"/>
-          <a:ext cx="1617224" cy="499159"/>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -840,15 +859,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>257736</xdr:colOff>
+      <xdr:colOff>246529</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>89647</xdr:rowOff>
+      <xdr:rowOff>112059</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>1389529</xdr:colOff>
+      <xdr:colOff>1378322</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>268941</xdr:rowOff>
+      <xdr:rowOff>291353</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -863,7 +882,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="257736" y="851647"/>
+          <a:off x="246529" y="672353"/>
           <a:ext cx="13794440" cy="2028265"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2164,7 +2183,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:H38"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="28.25" style="1" customWidth="1"/>
@@ -2180,14 +2199,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="44.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
       <c r="G1" s="3"/>
     </row>
     <row r="2" spans="1:7" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2246,7 +2265,7 @@
     </row>
     <row r="8" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="6"/>
@@ -2256,7 +2275,7 @@
     </row>
     <row r="9" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="6"/>
@@ -2272,7 +2291,7 @@
       <c r="C10" s="6"/>
       <c r="D10" s="7"/>
       <c r="E10" s="6" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F10" s="7"/>
     </row>
@@ -2284,7 +2303,7 @@
       <c r="C11" s="8"/>
       <c r="D11" s="9"/>
       <c r="E11" s="6" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F11" s="6"/>
     </row>
@@ -2296,299 +2315,326 @@
       <c r="C12" s="8"/>
       <c r="D12" s="9"/>
       <c r="E12" s="8" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F12" s="6"/>
     </row>
     <row r="13" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="10"/>
       <c r="D13" s="11"/>
       <c r="E13" s="8" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F13" s="8"/>
     </row>
     <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
       <c r="D14" s="11"/>
       <c r="E14" s="10" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F14" s="8"/>
     </row>
     <row r="15" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="B15" s="24"/>
-      <c r="C15" s="25"/>
-      <c r="D15" s="13"/>
+      <c r="A15" s="13"/>
+      <c r="B15" s="13"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="14"/>
       <c r="E15" s="10"/>
-      <c r="F15" s="26" t="s">
-        <v>12</v>
+      <c r="F15" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="29" t="s">
+      <c r="A16" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="D16" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" s="17" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="35" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" s="36"/>
+      <c r="C17" s="18"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="18"/>
+      <c r="F17" s="18"/>
+    </row>
+    <row r="18" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="37" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18" s="38"/>
+      <c r="C18" s="38"/>
+      <c r="D18" s="38"/>
+      <c r="E18" s="38"/>
+      <c r="F18" s="38"/>
+      <c r="G18" s="17" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="37" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" s="38"/>
+      <c r="C19" s="38"/>
+      <c r="D19" s="38"/>
+      <c r="E19" s="38"/>
+      <c r="F19" s="38"/>
+      <c r="G19" s="17" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" s="20"/>
+      <c r="C20" s="21"/>
+      <c r="D20" s="21"/>
+      <c r="E20" s="22"/>
+      <c r="F20" s="23"/>
+      <c r="G20" s="24"/>
+      <c r="H20" s="24"/>
+    </row>
+    <row r="21" spans="1:8" s="17" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="26" t="s">
+        <v>27</v>
+      </c>
+      <c r="B21" s="27"/>
+      <c r="C21" s="27"/>
+      <c r="D21" s="27"/>
+      <c r="E21" s="28"/>
+      <c r="F21" s="27"/>
+      <c r="G21" s="17" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="29"/>
+      <c r="B22" s="30"/>
+      <c r="C22" s="31"/>
+      <c r="D22" s="32"/>
+      <c r="E22" s="31"/>
+      <c r="F22" s="33"/>
+      <c r="G22" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="5"/>
+      <c r="G23" s="17" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" s="17" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="42" t="s">
+        <v>29</v>
+      </c>
+      <c r="B24" s="42"/>
+      <c r="C24" s="42"/>
+      <c r="D24" s="42"/>
+      <c r="E24" s="43"/>
+      <c r="F24" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="G24" s="17" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" s="17" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25" s="39"/>
+      <c r="C25" s="39"/>
+      <c r="D25" s="39"/>
+      <c r="E25" s="39"/>
+      <c r="F25" s="39"/>
+    </row>
+    <row r="26" spans="1:8" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26" s="40"/>
+      <c r="C26" s="40"/>
+      <c r="D26" s="40"/>
+      <c r="E26" s="40"/>
+      <c r="F26" s="40"/>
+    </row>
+    <row r="27" spans="1:8" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="40" t="s">
         <v>34</v>
       </c>
-      <c r="B16" s="29" t="s">
-        <v>33</v>
-      </c>
-      <c r="C16" s="29" t="s">
-        <v>32</v>
-      </c>
-      <c r="D16" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="E16" s="29" t="s">
-        <v>30</v>
-      </c>
-      <c r="F16" s="29" t="s">
-        <v>29</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" s="14" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="40" t="s">
+      <c r="B27" s="40"/>
+      <c r="C27" s="40"/>
+      <c r="D27" s="40"/>
+      <c r="E27" s="40"/>
+      <c r="F27" s="40"/>
+    </row>
+    <row r="28" spans="1:8" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="B28" s="40"/>
+      <c r="C28" s="40"/>
+      <c r="D28" s="40"/>
+      <c r="E28" s="40"/>
+      <c r="F28" s="40"/>
+    </row>
+    <row r="29" spans="1:8" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="B29" s="40"/>
+      <c r="C29" s="40"/>
+      <c r="D29" s="40"/>
+      <c r="E29" s="40"/>
+      <c r="F29" s="40"/>
+    </row>
+    <row r="30" spans="1:8" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="40" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30" s="40"/>
+      <c r="C30" s="40"/>
+      <c r="D30" s="40"/>
+      <c r="E30" s="40"/>
+      <c r="F30" s="40"/>
+    </row>
+    <row r="31" spans="1:8" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="40" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" s="40"/>
+      <c r="C31" s="40"/>
+      <c r="D31" s="40"/>
+      <c r="E31" s="40"/>
+      <c r="F31" s="40"/>
+    </row>
+    <row r="32" spans="1:8" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="40" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32" s="40"/>
+      <c r="C32" s="40"/>
+      <c r="D32" s="40"/>
+      <c r="E32" s="40"/>
+      <c r="F32" s="40"/>
+    </row>
+    <row r="33" spans="1:6" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="40" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" s="40"/>
+      <c r="C33" s="40"/>
+      <c r="D33" s="40"/>
+      <c r="E33" s="40"/>
+      <c r="F33" s="40"/>
+    </row>
+    <row r="34" spans="1:6" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="40" t="s">
+        <v>41</v>
+      </c>
+      <c r="B34" s="40"/>
+      <c r="C34" s="40"/>
+      <c r="D34" s="40"/>
+      <c r="E34" s="40"/>
+      <c r="F34" s="40"/>
+    </row>
+    <row r="35" spans="1:6" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="B35" s="40"/>
+      <c r="C35" s="40"/>
+      <c r="D35" s="40"/>
+      <c r="E35" s="40"/>
+      <c r="F35" s="40"/>
+    </row>
+    <row r="36" spans="1:6" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="40" t="s">
+        <v>43</v>
+      </c>
+      <c r="B36" s="40"/>
+      <c r="C36" s="40"/>
+      <c r="D36" s="40"/>
+      <c r="E36" s="40"/>
+      <c r="F36" s="40"/>
+    </row>
+    <row r="37" spans="1:6" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="40" t="s">
         <v>44</v>
       </c>
-      <c r="B17" s="41"/>
-      <c r="C17" s="31"/>
-      <c r="D17" s="31"/>
-      <c r="E17" s="31"/>
-      <c r="F17" s="31"/>
-    </row>
-    <row r="18" spans="1:8" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="B18" s="16"/>
-      <c r="C18" s="17"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="19"/>
-      <c r="G18" s="20"/>
-      <c r="H18" s="20"/>
-    </row>
-    <row r="19" spans="1:8" s="14" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="30" t="s">
-        <v>28</v>
-      </c>
-      <c r="B19" s="31"/>
-      <c r="C19" s="31"/>
-      <c r="D19" s="31"/>
-      <c r="E19" s="32"/>
-      <c r="F19" s="31"/>
-      <c r="G19" s="14" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B20" s="25"/>
-      <c r="E20" s="27"/>
-      <c r="F20" s="28"/>
-    </row>
-    <row r="21" spans="1:8" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="5"/>
-      <c r="B22" s="25"/>
-      <c r="E22" s="27"/>
-      <c r="F22" s="28"/>
-    </row>
-    <row r="23" spans="1:8" s="14" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="36" t="s">
-        <v>38</v>
-      </c>
-      <c r="B23" s="37"/>
-      <c r="C23" s="37"/>
-      <c r="D23" s="38"/>
-      <c r="E23" s="22"/>
-      <c r="F23" s="21" t="s">
-        <v>36</v>
-      </c>
-      <c r="G23" s="14" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" s="14" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="39" t="s">
-        <v>15</v>
-      </c>
-      <c r="B24" s="39"/>
-      <c r="C24" s="39"/>
-      <c r="D24" s="39"/>
-      <c r="E24" s="39"/>
-      <c r="F24" s="39"/>
-    </row>
-    <row r="25" spans="1:8" s="23" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="34" t="s">
-        <v>16</v>
-      </c>
-      <c r="B25" s="34"/>
-      <c r="C25" s="34"/>
-      <c r="D25" s="34"/>
-      <c r="E25" s="34"/>
-      <c r="F25" s="34"/>
-    </row>
-    <row r="26" spans="1:8" s="23" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="34" t="s">
-        <v>17</v>
-      </c>
-      <c r="B26" s="34"/>
-      <c r="C26" s="34"/>
-      <c r="D26" s="34"/>
-      <c r="E26" s="34"/>
-      <c r="F26" s="34"/>
-    </row>
-    <row r="27" spans="1:8" s="23" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="34" t="s">
-        <v>18</v>
-      </c>
-      <c r="B27" s="34"/>
-      <c r="C27" s="34"/>
-      <c r="D27" s="34"/>
-      <c r="E27" s="34"/>
-      <c r="F27" s="34"/>
-    </row>
-    <row r="28" spans="1:8" s="23" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="34" t="s">
-        <v>19</v>
-      </c>
-      <c r="B28" s="34"/>
-      <c r="C28" s="34"/>
-      <c r="D28" s="34"/>
-      <c r="E28" s="34"/>
-      <c r="F28" s="34"/>
-    </row>
-    <row r="29" spans="1:8" s="23" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="34" t="s">
-        <v>20</v>
-      </c>
-      <c r="B29" s="34"/>
-      <c r="C29" s="34"/>
-      <c r="D29" s="34"/>
-      <c r="E29" s="34"/>
-      <c r="F29" s="34"/>
-    </row>
-    <row r="30" spans="1:8" s="23" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="34" t="s">
-        <v>21</v>
-      </c>
-      <c r="B30" s="34"/>
-      <c r="C30" s="34"/>
-      <c r="D30" s="34"/>
-      <c r="E30" s="34"/>
-      <c r="F30" s="34"/>
-    </row>
-    <row r="31" spans="1:8" s="23" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="34" t="s">
-        <v>22</v>
-      </c>
-      <c r="B31" s="34"/>
-      <c r="C31" s="34"/>
-      <c r="D31" s="34"/>
-      <c r="E31" s="34"/>
-      <c r="F31" s="34"/>
-    </row>
-    <row r="32" spans="1:8" s="23" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="34" t="s">
-        <v>23</v>
-      </c>
-      <c r="B32" s="34"/>
-      <c r="C32" s="34"/>
-      <c r="D32" s="34"/>
-      <c r="E32" s="34"/>
-      <c r="F32" s="34"/>
-    </row>
-    <row r="33" spans="1:6" s="23" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="34" t="s">
-        <v>24</v>
-      </c>
-      <c r="B33" s="34"/>
-      <c r="C33" s="34"/>
-      <c r="D33" s="34"/>
-      <c r="E33" s="34"/>
-      <c r="F33" s="34"/>
-    </row>
-    <row r="34" spans="1:6" s="23" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="34" t="s">
-        <v>25</v>
-      </c>
-      <c r="B34" s="34"/>
-      <c r="C34" s="34"/>
-      <c r="D34" s="34"/>
-      <c r="E34" s="34"/>
-      <c r="F34" s="34"/>
-    </row>
-    <row r="35" spans="1:6" s="23" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="34" t="s">
-        <v>26</v>
-      </c>
-      <c r="B35" s="34"/>
-      <c r="C35" s="34"/>
-      <c r="D35" s="34"/>
-      <c r="E35" s="34"/>
-      <c r="F35" s="34"/>
-    </row>
-    <row r="36" spans="1:6" s="23" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="34" t="s">
-        <v>40</v>
-      </c>
-      <c r="B36" s="34"/>
-      <c r="C36" s="34"/>
-      <c r="D36" s="34"/>
-      <c r="E36" s="34"/>
-      <c r="F36" s="34"/>
-    </row>
-    <row r="37" spans="1:6" s="23" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="33" t="s">
-        <v>39</v>
-      </c>
-      <c r="B37" s="33"/>
-      <c r="C37" s="33"/>
-      <c r="D37" s="33"/>
-      <c r="E37" s="33"/>
-      <c r="F37" s="33"/>
+      <c r="B37" s="40"/>
+      <c r="C37" s="40"/>
+      <c r="D37" s="40"/>
+      <c r="E37" s="40"/>
+      <c r="F37" s="40"/>
+    </row>
+    <row r="38" spans="1:6" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="41" t="s">
+        <v>45</v>
+      </c>
+      <c r="B38" s="41"/>
+      <c r="C38" s="41"/>
+      <c r="D38" s="41"/>
+      <c r="E38" s="41"/>
+      <c r="F38" s="41"/>
     </row>
   </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A23:D23"/>
-    <mergeCell ref="A24:F24"/>
-    <mergeCell ref="A25:F25"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A26:F26"/>
-    <mergeCell ref="A27:F27"/>
-    <mergeCell ref="A28:F28"/>
-    <mergeCell ref="A29:F29"/>
+  <mergeCells count="19">
     <mergeCell ref="A35:F35"/>
+    <mergeCell ref="A36:F36"/>
     <mergeCell ref="A37:F37"/>
+    <mergeCell ref="A38:F38"/>
     <mergeCell ref="A30:F30"/>
     <mergeCell ref="A31:F31"/>
     <mergeCell ref="A32:F32"/>
     <mergeCell ref="A33:F33"/>
     <mergeCell ref="A34:F34"/>
-    <mergeCell ref="A36:F36"/>
+    <mergeCell ref="A25:F25"/>
+    <mergeCell ref="A26:F26"/>
+    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="A28:F28"/>
+    <mergeCell ref="A29:F29"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A24:D24"/>
   </mergeCells>
-  <phoneticPr fontId="14" type="noConversion"/>
+  <phoneticPr fontId="15" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="48" fitToHeight="0" orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>

--- a/template/견적서.xlsx
+++ b/template/견적서.xlsx
@@ -158,11 +158,11 @@
   </si>
   <si>
     <t>{{EMPTY_ROW}}</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>{{ITEM_END}}</t>
-    <phoneticPr fontId="15" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -212,71 +212,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color indexed="8"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="12"/>
-      <color indexed="12"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color indexed="8"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color indexed="10"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
@@ -290,6 +229,61 @@
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Noto Sans KR"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Noto Sans KR"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color indexed="10"/>
+      <name val="Noto Sans KR"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="Noto Sans KR"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Noto Sans KR"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color indexed="8"/>
+      <name val="Noto Sans KR"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color indexed="12"/>
+      <name val="Noto Sans KR"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color indexed="8"/>
+      <name val="Noto Sans KR"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
   </fonts>
   <fills count="4">
@@ -398,7 +392,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -412,122 +406,131 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="11" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="10" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2199,14 +2202,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="44.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
       <c r="G1" s="3"/>
     </row>
     <row r="2" spans="1:7" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -2264,92 +2267,92 @@
       <c r="G7" s="3"/>
     </row>
     <row r="8" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="5"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="7"/>
+      <c r="B8" s="24"/>
+      <c r="C8" s="25"/>
+      <c r="D8" s="26"/>
+      <c r="E8" s="25"/>
+      <c r="F8" s="26"/>
     </row>
     <row r="9" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="B9" s="5"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="7"/>
+      <c r="B9" s="24"/>
+      <c r="C9" s="25"/>
+      <c r="D9" s="26"/>
+      <c r="E9" s="25"/>
+      <c r="F9" s="26"/>
     </row>
     <row r="10" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="B10" s="5"/>
-      <c r="C10" s="6"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="6" t="s">
+      <c r="B10" s="24"/>
+      <c r="C10" s="25"/>
+      <c r="D10" s="26"/>
+      <c r="E10" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="F10" s="7"/>
+      <c r="F10" s="26"/>
     </row>
     <row r="11" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="B11" s="5"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="6" t="s">
+      <c r="B11" s="24"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="28"/>
+      <c r="E11" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="F11" s="6"/>
+      <c r="F11" s="25"/>
     </row>
     <row r="12" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="B12" s="5"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="8" t="s">
+      <c r="B12" s="24"/>
+      <c r="C12" s="27"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="F12" s="6"/>
+      <c r="F12" s="25"/>
     </row>
     <row r="13" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="5"/>
-      <c r="C13" s="10"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="8" t="s">
+      <c r="B13" s="24"/>
+      <c r="C13" s="29"/>
+      <c r="D13" s="30"/>
+      <c r="E13" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="F13" s="8"/>
+      <c r="F13" s="27"/>
     </row>
     <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="12" t="s">
+      <c r="A14" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="10" t="s">
+      <c r="B14" s="24"/>
+      <c r="C14" s="24"/>
+      <c r="D14" s="30"/>
+      <c r="E14" s="29" t="s">
         <v>12</v>
       </c>
-      <c r="F14" s="8"/>
+      <c r="F14" s="27"/>
     </row>
     <row r="15" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="13"/>
-      <c r="B15" s="13"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="10"/>
-      <c r="F15" s="15" t="s">
+      <c r="A15" s="32"/>
+      <c r="B15" s="32"/>
+      <c r="C15" s="24"/>
+      <c r="D15" s="33"/>
+      <c r="E15" s="29"/>
+      <c r="F15" s="34" t="s">
         <v>14</v>
       </c>
       <c r="G15" s="1" t="s">
@@ -2357,107 +2360,112 @@
       </c>
     </row>
     <row r="16" spans="1:7" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="16" t="s">
+      <c r="A16" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="16" t="s">
+      <c r="B16" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="C16" s="16" t="s">
+      <c r="C16" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="D16" s="16" t="s">
+      <c r="D16" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="E16" s="16" t="s">
+      <c r="E16" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="F16" s="16" t="s">
+      <c r="F16" s="15" t="s">
         <v>20</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="1:8" s="17" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="35" t="s">
+    <row r="17" spans="1:8" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="B17" s="36"/>
+      <c r="B17" s="17"/>
       <c r="C17" s="18"/>
       <c r="D17" s="18"/>
       <c r="E17" s="18"/>
       <c r="F17" s="18"/>
     </row>
     <row r="18" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="37" t="s">
+      <c r="A18" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="B18" s="38"/>
-      <c r="C18" s="38"/>
-      <c r="D18" s="38"/>
-      <c r="E18" s="38"/>
-      <c r="F18" s="38"/>
-      <c r="G18" s="17" t="s">
+      <c r="B18" s="20"/>
+      <c r="C18" s="20"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="20"/>
+      <c r="F18" s="20"/>
+      <c r="G18" s="5" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="37" t="s">
+      <c r="A19" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="B19" s="38"/>
-      <c r="C19" s="38"/>
-      <c r="D19" s="38"/>
-      <c r="E19" s="38"/>
-      <c r="F19" s="38"/>
-      <c r="G19" s="17" t="s">
+      <c r="B19" s="20"/>
+      <c r="C19" s="20"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="20"/>
+      <c r="F19" s="20"/>
+      <c r="G19" s="5" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="19" t="s">
+      <c r="A20" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="B20" s="20"/>
-      <c r="C20" s="21"/>
-      <c r="D20" s="21"/>
-      <c r="E20" s="22"/>
-      <c r="F20" s="23"/>
-      <c r="G20" s="24"/>
-      <c r="H20" s="24"/>
-    </row>
-    <row r="21" spans="1:8" s="17" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="26" t="s">
+      <c r="B20" s="10"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="14"/>
+      <c r="G20" s="6"/>
+      <c r="H20" s="6"/>
+    </row>
+    <row r="21" spans="1:8" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="B21" s="27"/>
-      <c r="C21" s="27"/>
-      <c r="D21" s="27"/>
-      <c r="E21" s="28"/>
-      <c r="F21" s="27"/>
-      <c r="G21" s="17" t="s">
+      <c r="B21" s="22"/>
+      <c r="C21" s="22"/>
+      <c r="D21" s="22"/>
+      <c r="E21" s="23"/>
+      <c r="F21" s="22"/>
+      <c r="G21" s="5" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="29"/>
-      <c r="B22" s="30"/>
-      <c r="C22" s="31"/>
-      <c r="D22" s="32"/>
-      <c r="E22" s="31"/>
-      <c r="F22" s="33"/>
-      <c r="G22" s="17" t="s">
+      <c r="A22" s="35"/>
+      <c r="B22" s="36"/>
+      <c r="C22" s="37"/>
+      <c r="D22" s="38"/>
+      <c r="E22" s="37"/>
+      <c r="F22" s="39"/>
+      <c r="G22" s="5" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="5"/>
-      <c r="G23" s="17" t="s">
+      <c r="A23" s="24"/>
+      <c r="B23" s="40"/>
+      <c r="C23" s="40"/>
+      <c r="D23" s="41"/>
+      <c r="E23" s="40"/>
+      <c r="F23" s="41"/>
+      <c r="G23" s="5" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="24" spans="1:8" s="17" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="42" t="s">
         <v>29</v>
       </c>
@@ -2465,152 +2473,152 @@
       <c r="C24" s="42"/>
       <c r="D24" s="42"/>
       <c r="E24" s="43"/>
-      <c r="F24" s="16" t="s">
+      <c r="F24" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="G24" s="17" t="s">
+      <c r="G24" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="25" spans="1:8" s="17" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="39" t="s">
+    <row r="25" spans="1:8" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="B25" s="39"/>
-      <c r="C25" s="39"/>
-      <c r="D25" s="39"/>
-      <c r="E25" s="39"/>
-      <c r="F25" s="39"/>
-    </row>
-    <row r="26" spans="1:8" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="40" t="s">
+      <c r="B25" s="44"/>
+      <c r="C25" s="44"/>
+      <c r="D25" s="44"/>
+      <c r="E25" s="44"/>
+      <c r="F25" s="44"/>
+    </row>
+    <row r="26" spans="1:8" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="45" t="s">
         <v>33</v>
       </c>
-      <c r="B26" s="40"/>
-      <c r="C26" s="40"/>
-      <c r="D26" s="40"/>
-      <c r="E26" s="40"/>
-      <c r="F26" s="40"/>
-    </row>
-    <row r="27" spans="1:8" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="40" t="s">
+      <c r="B26" s="45"/>
+      <c r="C26" s="45"/>
+      <c r="D26" s="45"/>
+      <c r="E26" s="45"/>
+      <c r="F26" s="45"/>
+    </row>
+    <row r="27" spans="1:8" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="45" t="s">
         <v>34</v>
       </c>
-      <c r="B27" s="40"/>
-      <c r="C27" s="40"/>
-      <c r="D27" s="40"/>
-      <c r="E27" s="40"/>
-      <c r="F27" s="40"/>
-    </row>
-    <row r="28" spans="1:8" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="40" t="s">
+      <c r="B27" s="45"/>
+      <c r="C27" s="45"/>
+      <c r="D27" s="45"/>
+      <c r="E27" s="45"/>
+      <c r="F27" s="45"/>
+    </row>
+    <row r="28" spans="1:8" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="45" t="s">
         <v>35</v>
       </c>
-      <c r="B28" s="40"/>
-      <c r="C28" s="40"/>
-      <c r="D28" s="40"/>
-      <c r="E28" s="40"/>
-      <c r="F28" s="40"/>
-    </row>
-    <row r="29" spans="1:8" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="40" t="s">
+      <c r="B28" s="45"/>
+      <c r="C28" s="45"/>
+      <c r="D28" s="45"/>
+      <c r="E28" s="45"/>
+      <c r="F28" s="45"/>
+    </row>
+    <row r="29" spans="1:8" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="B29" s="40"/>
-      <c r="C29" s="40"/>
-      <c r="D29" s="40"/>
-      <c r="E29" s="40"/>
-      <c r="F29" s="40"/>
-    </row>
-    <row r="30" spans="1:8" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="40" t="s">
+      <c r="B29" s="45"/>
+      <c r="C29" s="45"/>
+      <c r="D29" s="45"/>
+      <c r="E29" s="45"/>
+      <c r="F29" s="45"/>
+    </row>
+    <row r="30" spans="1:8" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="45" t="s">
         <v>37</v>
       </c>
-      <c r="B30" s="40"/>
-      <c r="C30" s="40"/>
-      <c r="D30" s="40"/>
-      <c r="E30" s="40"/>
-      <c r="F30" s="40"/>
-    </row>
-    <row r="31" spans="1:8" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="40" t="s">
+      <c r="B30" s="45"/>
+      <c r="C30" s="45"/>
+      <c r="D30" s="45"/>
+      <c r="E30" s="45"/>
+      <c r="F30" s="45"/>
+    </row>
+    <row r="31" spans="1:8" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="45" t="s">
         <v>38</v>
       </c>
-      <c r="B31" s="40"/>
-      <c r="C31" s="40"/>
-      <c r="D31" s="40"/>
-      <c r="E31" s="40"/>
-      <c r="F31" s="40"/>
-    </row>
-    <row r="32" spans="1:8" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="40" t="s">
+      <c r="B31" s="45"/>
+      <c r="C31" s="45"/>
+      <c r="D31" s="45"/>
+      <c r="E31" s="45"/>
+      <c r="F31" s="45"/>
+    </row>
+    <row r="32" spans="1:8" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="B32" s="40"/>
-      <c r="C32" s="40"/>
-      <c r="D32" s="40"/>
-      <c r="E32" s="40"/>
-      <c r="F32" s="40"/>
-    </row>
-    <row r="33" spans="1:6" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="40" t="s">
+      <c r="B32" s="45"/>
+      <c r="C32" s="45"/>
+      <c r="D32" s="45"/>
+      <c r="E32" s="45"/>
+      <c r="F32" s="45"/>
+    </row>
+    <row r="33" spans="1:6" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="45" t="s">
         <v>40</v>
       </c>
-      <c r="B33" s="40"/>
-      <c r="C33" s="40"/>
-      <c r="D33" s="40"/>
-      <c r="E33" s="40"/>
-      <c r="F33" s="40"/>
-    </row>
-    <row r="34" spans="1:6" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="40" t="s">
+      <c r="B33" s="45"/>
+      <c r="C33" s="45"/>
+      <c r="D33" s="45"/>
+      <c r="E33" s="45"/>
+      <c r="F33" s="45"/>
+    </row>
+    <row r="34" spans="1:6" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="45" t="s">
         <v>41</v>
       </c>
-      <c r="B34" s="40"/>
-      <c r="C34" s="40"/>
-      <c r="D34" s="40"/>
-      <c r="E34" s="40"/>
-      <c r="F34" s="40"/>
-    </row>
-    <row r="35" spans="1:6" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="40" t="s">
+      <c r="B34" s="45"/>
+      <c r="C34" s="45"/>
+      <c r="D34" s="45"/>
+      <c r="E34" s="45"/>
+      <c r="F34" s="45"/>
+    </row>
+    <row r="35" spans="1:6" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="45" t="s">
         <v>42</v>
       </c>
-      <c r="B35" s="40"/>
-      <c r="C35" s="40"/>
-      <c r="D35" s="40"/>
-      <c r="E35" s="40"/>
-      <c r="F35" s="40"/>
-    </row>
-    <row r="36" spans="1:6" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="40" t="s">
+      <c r="B35" s="45"/>
+      <c r="C35" s="45"/>
+      <c r="D35" s="45"/>
+      <c r="E35" s="45"/>
+      <c r="F35" s="45"/>
+    </row>
+    <row r="36" spans="1:6" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="B36" s="40"/>
-      <c r="C36" s="40"/>
-      <c r="D36" s="40"/>
-      <c r="E36" s="40"/>
-      <c r="F36" s="40"/>
-    </row>
-    <row r="37" spans="1:6" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="40" t="s">
+      <c r="B36" s="45"/>
+      <c r="C36" s="45"/>
+      <c r="D36" s="45"/>
+      <c r="E36" s="45"/>
+      <c r="F36" s="45"/>
+    </row>
+    <row r="37" spans="1:6" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="45" t="s">
         <v>44</v>
       </c>
-      <c r="B37" s="40"/>
-      <c r="C37" s="40"/>
-      <c r="D37" s="40"/>
-      <c r="E37" s="40"/>
-      <c r="F37" s="40"/>
-    </row>
-    <row r="38" spans="1:6" s="25" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="41" t="s">
+      <c r="B37" s="45"/>
+      <c r="C37" s="45"/>
+      <c r="D37" s="45"/>
+      <c r="E37" s="45"/>
+      <c r="F37" s="45"/>
+    </row>
+    <row r="38" spans="1:6" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="46" t="s">
         <v>45</v>
       </c>
-      <c r="B38" s="41"/>
-      <c r="C38" s="41"/>
-      <c r="D38" s="41"/>
-      <c r="E38" s="41"/>
-      <c r="F38" s="41"/>
+      <c r="B38" s="46"/>
+      <c r="C38" s="46"/>
+      <c r="D38" s="46"/>
+      <c r="E38" s="46"/>
+      <c r="F38" s="46"/>
     </row>
   </sheetData>
   <mergeCells count="19">
@@ -2634,7 +2642,7 @@
     <mergeCell ref="A19:F19"/>
     <mergeCell ref="A24:D24"/>
   </mergeCells>
-  <phoneticPr fontId="15" type="noConversion"/>
+  <phoneticPr fontId="7" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="48" fitToHeight="0" orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
